--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>67.9366666666667</v>
+        <v>68.4191891891892</v>
       </c>
       <c r="C167" t="n">
-        <v>61.8086049271293</v>
+        <v>62.2476026793942</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>68.4191891891892</v>
+        <v>68.8959523809524</v>
       </c>
       <c r="C167" t="n">
-        <v>62.2476026793942</v>
+        <v>62.6813606073195</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>68.8959523809524</v>
+        <v>71.0031914893617</v>
       </c>
       <c r="C167" t="n">
-        <v>62.6813606073195</v>
+        <v>64.5985213384711</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>71.0031914893617</v>
+        <v>73.5503846153846</v>
       </c>
       <c r="C167" t="n">
-        <v>64.5985213384711</v>
+        <v>66.8757130109317</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>73.5503846153846</v>
+        <v>76.9185964912281</v>
       </c>
       <c r="C167" t="n">
-        <v>66.8757130109317</v>
+        <v>69.9382608405158</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>76.9185964912281</v>
+        <v>79.9783870967742</v>
       </c>
       <c r="C167" t="n">
-        <v>69.9382608405158</v>
+        <v>72.7203765218966</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>79.9783870967742</v>
+        <v>82.0387692307692</v>
       </c>
       <c r="C167" t="n">
-        <v>72.7203765218966</v>
+        <v>74.5937796999553</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>82.0387692307692</v>
+        <v>85.0602857142857</v>
       </c>
       <c r="C167" t="n">
-        <v>74.5937796999553</v>
+        <v>77.3410946224551</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>85.0602857142857</v>
+        <v>86.7533333333333</v>
       </c>
       <c r="C167" t="n">
-        <v>77.3410946224551</v>
+        <v>78.7069616666667</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>86.7533333333333</v>
+        <v>89.8733333333333</v>
       </c>
       <c r="C167" t="n">
-        <v>78.7069616666667</v>
+        <v>81.5375816666667</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>89.8733333333333</v>
+        <v>92.8644660194175</v>
       </c>
       <c r="C167" t="n">
-        <v>81.5375816666667</v>
+        <v>84.1083026815579</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>92.8644660194175</v>
+        <v>91.6672357723577</v>
       </c>
       <c r="C167" t="n">
-        <v>84.1083026815579</v>
+        <v>82.8403654220172</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>91.6672357723577</v>
+        <v>90.79328125</v>
       </c>
       <c r="C167" t="n">
-        <v>82.8403654220172</v>
+        <v>82.0505661945798</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>90.79328125</v>
+        <v>90.2273684210526</v>
       </c>
       <c r="C167" t="n">
-        <v>82.0505661945798</v>
+        <v>81.5391465455415</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>90.2273684210526</v>
+        <v>90.0017391304348</v>
       </c>
       <c r="C167" t="n">
-        <v>81.5391465455415</v>
+        <v>81.2559237994696</v>
       </c>
     </row>
   </sheetData>
